--- a/Dowling/dowling-vs-johnston-offense.xlsx
+++ b/Dowling/dowling-vs-johnston-offense.xlsx
@@ -5,7 +5,7 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="Re3e72eba459d4e21"/>
+    <sheet name="Sheet1" sheetId="1" r:id="Rb274df3ffd90458d"/>
   </sheets>
 </workbook>
 </file>
@@ -58,6 +58,21 @@
     <t>PASS ZONE</t>
   </si>
   <si>
+    <t>BACKFIELD</t>
+  </si>
+  <si>
+    <t>DEF FRONT</t>
+  </si>
+  <si>
+    <t>FRONT MOVEMENT</t>
+  </si>
+  <si>
+    <t>COVERAGE</t>
+  </si>
+  <si>
+    <t>BLITZ</t>
+  </si>
+  <si>
     <t>KICK YARDS</t>
   </si>
   <si>
@@ -251,6 +266,9 @@
   </si>
   <si>
     <t>Complete, Fumble</t>
+  </si>
+  <si>
+    <t>G</t>
   </si>
   <si>
     <t>Fumble</t>
@@ -317,7 +335,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:X153"/>
+  <dimension ref="A1:AC153"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -392,6 +410,21 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -401,7 +434,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -410,13 +443,13 @@
         <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -427,7 +460,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -439,25 +472,28 @@
         <v>-20</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J3">
         <v>3</v>
       </c>
       <c r="K3" t="s">
-        <v>31</v>
-      </c>
-      <c r="S3" t="s">
-        <v>32</v>
-      </c>
-      <c r="T3" t="s">
-        <v>33</v>
+        <v>36</v>
+      </c>
+      <c r="P3" t="s">
+        <v>29</v>
+      </c>
+      <c r="X3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -468,7 +504,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -480,25 +516,25 @@
         <v>-23</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I4" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>31</v>
-      </c>
-      <c r="S4" t="s">
         <v>36</v>
       </c>
-      <c r="T4" t="s">
-        <v>37</v>
+      <c r="X4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="5">
@@ -509,7 +545,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -521,25 +557,25 @@
         <v>-23</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J5">
         <v>2</v>
       </c>
       <c r="K5" t="s">
-        <v>31</v>
-      </c>
-      <c r="S5" t="s">
         <v>36</v>
       </c>
-      <c r="T5" t="s">
-        <v>39</v>
+      <c r="X5" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +586,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -562,13 +598,13 @@
         <v>-25</v>
       </c>
       <c r="G6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H6" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -579,7 +615,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -591,25 +627,28 @@
         <v>50</v>
       </c>
       <c r="G7" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H7" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I7" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J7">
         <v>9</v>
       </c>
       <c r="K7" t="s">
-        <v>43</v>
-      </c>
-      <c r="S7" t="s">
-        <v>36</v>
-      </c>
-      <c r="T7" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="P7" t="s">
+        <v>29</v>
+      </c>
+      <c r="X7" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="8">
@@ -620,7 +659,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -632,25 +671,28 @@
         <v>41</v>
       </c>
       <c r="G8" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H8" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I8" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J8">
         <v>10</v>
       </c>
       <c r="K8" t="s">
-        <v>43</v>
-      </c>
-      <c r="S8" t="s">
-        <v>45</v>
-      </c>
-      <c r="T8" t="s">
-        <v>46</v>
+        <v>48</v>
+      </c>
+      <c r="P8" t="s">
+        <v>29</v>
+      </c>
+      <c r="X8" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="9">
@@ -661,7 +703,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -673,25 +715,25 @@
         <v>31</v>
       </c>
       <c r="G9" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H9" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I9" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J9">
         <v>2</v>
       </c>
       <c r="K9" t="s">
-        <v>31</v>
-      </c>
-      <c r="S9" t="s">
-        <v>47</v>
-      </c>
-      <c r="T9" t="s">
-        <v>48</v>
+        <v>36</v>
+      </c>
+      <c r="X9" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="10">
@@ -702,7 +744,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D10">
         <v>2</v>
@@ -714,28 +756,31 @@
         <v>29</v>
       </c>
       <c r="G10" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H10" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I10" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>31</v>
-      </c>
-      <c r="S10" t="s">
-        <v>49</v>
-      </c>
-      <c r="T10" t="s">
-        <v>50</v>
-      </c>
-      <c r="V10" t="s">
-        <v>25</v>
+        <v>36</v>
+      </c>
+      <c r="P10" t="s">
+        <v>29</v>
+      </c>
+      <c r="X10" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="11">
@@ -746,7 +791,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D11">
         <v>3</v>
@@ -758,25 +803,25 @@
         <v>29</v>
       </c>
       <c r="G11" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H11" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I11" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="J11">
         <v>15</v>
       </c>
       <c r="K11" t="s">
-        <v>43</v>
-      </c>
-      <c r="S11" t="s">
-        <v>52</v>
-      </c>
-      <c r="T11" t="s">
-        <v>53</v>
+        <v>48</v>
+      </c>
+      <c r="X11" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="12">
@@ -787,7 +832,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -799,25 +844,25 @@
         <v>14</v>
       </c>
       <c r="G12" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H12" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I12" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J12">
         <v>3</v>
       </c>
       <c r="K12" t="s">
-        <v>31</v>
-      </c>
-      <c r="S12" t="s">
-        <v>45</v>
-      </c>
-      <c r="T12" t="s">
-        <v>46</v>
+        <v>36</v>
+      </c>
+      <c r="X12" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="13">
@@ -828,7 +873,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -840,25 +885,25 @@
         <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H13" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I13" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J13">
         <v>4</v>
       </c>
       <c r="K13" t="s">
-        <v>43</v>
-      </c>
-      <c r="S13" t="s">
-        <v>47</v>
-      </c>
-      <c r="T13" t="s">
         <v>48</v>
+      </c>
+      <c r="X13" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -869,7 +914,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D14">
         <v>3</v>
@@ -881,25 +926,28 @@
         <v>8</v>
       </c>
       <c r="G14" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H14" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I14" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J14">
         <v>3</v>
       </c>
       <c r="K14" t="s">
-        <v>31</v>
-      </c>
-      <c r="S14" t="s">
-        <v>54</v>
-      </c>
-      <c r="T14" t="s">
-        <v>55</v>
+        <v>36</v>
+      </c>
+      <c r="P14" t="s">
+        <v>29</v>
+      </c>
+      <c r="X14" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -910,7 +958,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D15">
         <v>4</v>
@@ -922,22 +970,22 @@
         <v>6</v>
       </c>
       <c r="G15" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H15" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I15" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>31</v>
-      </c>
-      <c r="T15" t="s">
-        <v>56</v>
+        <v>36</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="16">
@@ -948,7 +996,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -960,13 +1008,13 @@
         <v>-6</v>
       </c>
       <c r="G16" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H16" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I16" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -977,7 +1025,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -986,13 +1034,13 @@
         <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H17" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I17" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -1003,7 +1051,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D18">
         <v>3</v>
@@ -1012,7 +1060,7 @@
         <v>10</v>
       </c>
       <c r="G18" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
@@ -1023,7 +1071,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D19">
         <v>3</v>
@@ -1032,13 +1080,13 @@
         <v>5</v>
       </c>
       <c r="G19" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H19" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I19" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -1049,7 +1097,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D20">
         <v>4</v>
@@ -1058,13 +1106,13 @@
         <v>5</v>
       </c>
       <c r="G20" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H20" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I20" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21">
@@ -1075,7 +1123,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1084,25 +1132,28 @@
         <v>10</v>
       </c>
       <c r="G21" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H21" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I21" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J21">
         <v>7</v>
       </c>
       <c r="K21" t="s">
-        <v>43</v>
-      </c>
-      <c r="S21" t="s">
-        <v>36</v>
-      </c>
-      <c r="T21" t="s">
-        <v>59</v>
+        <v>48</v>
+      </c>
+      <c r="P21" t="s">
+        <v>29</v>
+      </c>
+      <c r="X21" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="22">
@@ -1113,7 +1164,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D22">
         <v>2</v>
@@ -1122,25 +1173,25 @@
         <v>4</v>
       </c>
       <c r="G22" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H22" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I22" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J22">
         <v>4</v>
       </c>
       <c r="K22" t="s">
-        <v>43</v>
-      </c>
-      <c r="S22" t="s">
-        <v>60</v>
-      </c>
-      <c r="T22" t="s">
-        <v>61</v>
+        <v>48</v>
+      </c>
+      <c r="X22" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="23">
@@ -1151,7 +1202,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -1163,25 +1214,25 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H23" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I23" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J23">
         <v>6</v>
       </c>
       <c r="K23" t="s">
-        <v>43</v>
-      </c>
-      <c r="S23" t="s">
-        <v>47</v>
-      </c>
-      <c r="T23" t="s">
         <v>48</v>
+      </c>
+      <c r="X23" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="24">
@@ -1192,7 +1243,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D24">
         <v>2</v>
@@ -1204,25 +1255,25 @@
         <v>10</v>
       </c>
       <c r="G24" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H24" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I24" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="J24">
         <v>10</v>
       </c>
       <c r="K24" t="s">
-        <v>43</v>
-      </c>
-      <c r="S24" t="s">
-        <v>52</v>
-      </c>
-      <c r="T24" t="s">
-        <v>63</v>
+        <v>48</v>
+      </c>
+      <c r="X24" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="25">
@@ -1233,7 +1284,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -1245,13 +1296,13 @@
         <v>-1</v>
       </c>
       <c r="G25" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H25" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I25" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26">
@@ -1262,7 +1313,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -1271,13 +1322,13 @@
         <v>10</v>
       </c>
       <c r="G26" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H26" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I26" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27">
@@ -1288,7 +1339,7 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -1297,13 +1348,13 @@
         <v>10</v>
       </c>
       <c r="G27" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H27" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I27" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28">
@@ -1314,7 +1365,7 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D28">
         <v>2</v>
@@ -1323,13 +1374,13 @@
         <v>7</v>
       </c>
       <c r="G28" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H28" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I28" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29">
@@ -1340,7 +1391,7 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D29">
         <v>3</v>
@@ -1349,13 +1400,13 @@
         <v>7</v>
       </c>
       <c r="G29" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H29" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I29" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30">
@@ -1366,7 +1417,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -1375,13 +1426,13 @@
         <v>10</v>
       </c>
       <c r="G30" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H30" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I30" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31">
@@ -1392,7 +1443,7 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -1401,13 +1452,13 @@
         <v>10</v>
       </c>
       <c r="G31" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H31" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I31" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32">
@@ -1418,7 +1469,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D32">
         <v>2</v>
@@ -1427,13 +1478,13 @@
         <v>12</v>
       </c>
       <c r="G32" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H32" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I32" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33">
@@ -1444,7 +1495,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -1453,13 +1504,13 @@
         <v>10</v>
       </c>
       <c r="G33" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H33" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I33" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34">
@@ -1470,7 +1521,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -1479,13 +1530,13 @@
         <v>10</v>
       </c>
       <c r="G34" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H34" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I34" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35">
@@ -1496,7 +1547,7 @@
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -1508,25 +1559,25 @@
         <v>-20</v>
       </c>
       <c r="G35" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H35" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I35" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="J35">
         <v>80</v>
       </c>
       <c r="K35" t="s">
-        <v>43</v>
-      </c>
-      <c r="S35" t="s">
-        <v>47</v>
-      </c>
-      <c r="T35" t="s">
-        <v>70</v>
+        <v>48</v>
+      </c>
+      <c r="X35" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="36">
@@ -1537,7 +1588,7 @@
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -1549,13 +1600,13 @@
         <v>3</v>
       </c>
       <c r="G36" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H36" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I36" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37">
@@ -1566,7 +1617,7 @@
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -1575,13 +1626,13 @@
         <v>10</v>
       </c>
       <c r="G37" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H37" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I37" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="38">
@@ -1592,7 +1643,7 @@
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -1601,13 +1652,13 @@
         <v>10</v>
       </c>
       <c r="G38" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H38" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I38" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39">
@@ -1618,7 +1669,7 @@
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D39">
         <v>2</v>
@@ -1627,13 +1678,13 @@
         <v>8</v>
       </c>
       <c r="G39" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H39" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I39" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40">
@@ -1644,7 +1695,7 @@
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -1653,13 +1704,13 @@
         <v>10</v>
       </c>
       <c r="G40" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H40" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I40" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41">
@@ -1670,7 +1721,7 @@
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D41">
         <v>2</v>
@@ -1679,16 +1730,16 @@
         <v>10</v>
       </c>
       <c r="G41" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H41" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I41" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K41" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="42">
@@ -1699,7 +1750,7 @@
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -1711,25 +1762,25 @@
         <v>-39</v>
       </c>
       <c r="G42" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H42" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I42" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="J42">
         <v>61</v>
       </c>
       <c r="K42" t="s">
-        <v>43</v>
-      </c>
-      <c r="S42" t="s">
-        <v>54</v>
-      </c>
-      <c r="T42" t="s">
-        <v>72</v>
+        <v>48</v>
+      </c>
+      <c r="X42" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="43">
@@ -1740,7 +1791,7 @@
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -1752,13 +1803,13 @@
         <v>3</v>
       </c>
       <c r="G43" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H43" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I43" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44">
@@ -1769,7 +1820,7 @@
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -1778,13 +1829,13 @@
         <v>10</v>
       </c>
       <c r="G44" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H44" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I44" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45">
@@ -1795,7 +1846,7 @@
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -1804,13 +1855,13 @@
         <v>10</v>
       </c>
       <c r="G45" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H45" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I45" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46">
@@ -1821,7 +1872,7 @@
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D46">
         <v>2</v>
@@ -1830,13 +1881,13 @@
         <v>10</v>
       </c>
       <c r="G46" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H46" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I46" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47">
@@ -1847,7 +1898,7 @@
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D47">
         <v>3</v>
@@ -1856,13 +1907,13 @@
         <v>2</v>
       </c>
       <c r="G47" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H47" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I47" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48">
@@ -1873,7 +1924,7 @@
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -1882,7 +1933,7 @@
         <v>10</v>
       </c>
       <c r="G48" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49">
@@ -1893,7 +1944,7 @@
         <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -1902,13 +1953,13 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H49" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I49" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="50">
@@ -1919,7 +1970,7 @@
         <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D50">
         <v>2</v>
@@ -1928,13 +1979,13 @@
         <v>19</v>
       </c>
       <c r="G50" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H50" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I50" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="51">
@@ -1945,7 +1996,7 @@
         <v>1</v>
       </c>
       <c r="C51" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D51">
         <v>3</v>
@@ -1954,13 +2005,13 @@
         <v>20</v>
       </c>
       <c r="G51" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H51" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I51" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="52">
@@ -1971,7 +2022,7 @@
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -1980,13 +2031,13 @@
         <v>10</v>
       </c>
       <c r="G52" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H52" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I52" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="53">
@@ -1997,7 +2048,7 @@
         <v>1</v>
       </c>
       <c r="C53" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -2006,13 +2057,13 @@
         <v>10</v>
       </c>
       <c r="G53" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H53" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I53" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54">
@@ -2023,7 +2074,7 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -2032,28 +2083,31 @@
         <v>5</v>
       </c>
       <c r="G54" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H54" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I54" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J54">
         <v>5</v>
       </c>
       <c r="K54" t="s">
-        <v>43</v>
-      </c>
-      <c r="S54" t="s">
-        <v>36</v>
-      </c>
-      <c r="T54" t="s">
-        <v>74</v>
-      </c>
-      <c r="V54" t="s">
-        <v>42</v>
+        <v>48</v>
+      </c>
+      <c r="P54" t="s">
+        <v>29</v>
+      </c>
+      <c r="X54" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="55">
@@ -2064,7 +2118,7 @@
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D55">
         <v>2</v>
@@ -2073,25 +2127,25 @@
         <v>5</v>
       </c>
       <c r="G55" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H55" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I55" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J55">
         <v>9</v>
       </c>
       <c r="K55" t="s">
-        <v>43</v>
-      </c>
-      <c r="S55" t="s">
-        <v>47</v>
-      </c>
-      <c r="T55" t="s">
-        <v>70</v>
+        <v>48</v>
+      </c>
+      <c r="X55" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="56">
@@ -2102,7 +2156,7 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -2114,25 +2168,25 @@
         <v>-33</v>
       </c>
       <c r="G56" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H56" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I56" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J56">
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>31</v>
-      </c>
-      <c r="S56" t="s">
-        <v>54</v>
-      </c>
-      <c r="T56" t="s">
-        <v>72</v>
+        <v>36</v>
+      </c>
+      <c r="X56" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="57">
@@ -2143,7 +2197,7 @@
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D57">
         <v>2</v>
@@ -2155,25 +2209,28 @@
         <v>-33</v>
       </c>
       <c r="G57" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H57" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I57" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J57">
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>31</v>
-      </c>
-      <c r="S57" t="s">
         <v>36</v>
       </c>
-      <c r="T57" t="s">
-        <v>37</v>
+      <c r="P57" t="s">
+        <v>29</v>
+      </c>
+      <c r="X57" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="58">
@@ -2184,7 +2241,7 @@
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D58">
         <v>3</v>
@@ -2196,28 +2253,31 @@
         <v>-32</v>
       </c>
       <c r="G58" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H58" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I58" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J58">
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>31</v>
-      </c>
-      <c r="S58" t="s">
-        <v>49</v>
-      </c>
-      <c r="T58" t="s">
-        <v>75</v>
-      </c>
-      <c r="V58" t="s">
-        <v>42</v>
+        <v>36</v>
+      </c>
+      <c r="P58" t="s">
+        <v>29</v>
+      </c>
+      <c r="X58" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA58" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="59">
@@ -2228,7 +2288,7 @@
         <v>2</v>
       </c>
       <c r="C59" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D59">
         <v>4</v>
@@ -2240,13 +2300,13 @@
         <v>-34</v>
       </c>
       <c r="G59" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H59" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I59" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="60">
@@ -2257,7 +2317,7 @@
         <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -2266,13 +2326,13 @@
         <v>10</v>
       </c>
       <c r="G60" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H60" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I60" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="61">
@@ -2283,7 +2343,7 @@
         <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -2292,13 +2352,13 @@
         <v>10</v>
       </c>
       <c r="G61" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H61" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I61" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="62">
@@ -2309,7 +2369,7 @@
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -2318,13 +2378,13 @@
         <v>10</v>
       </c>
       <c r="G62" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H62" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I62" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="63">
@@ -2335,7 +2395,7 @@
         <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -2344,28 +2404,28 @@
         <v>5</v>
       </c>
       <c r="G63" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H63" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I63" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J63">
         <v>5</v>
       </c>
       <c r="K63" t="s">
-        <v>43</v>
-      </c>
-      <c r="S63" t="s">
-        <v>54</v>
-      </c>
-      <c r="T63" t="s">
-        <v>77</v>
-      </c>
-      <c r="V63" t="s">
-        <v>42</v>
+        <v>48</v>
+      </c>
+      <c r="X63" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA63" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="64">
@@ -2376,7 +2436,7 @@
         <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D64">
         <v>2</v>
@@ -2385,25 +2445,28 @@
         <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H64" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I64" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J64">
         <v>5</v>
       </c>
       <c r="K64" t="s">
-        <v>43</v>
-      </c>
-      <c r="S64" t="s">
-        <v>32</v>
-      </c>
-      <c r="T64" t="s">
-        <v>78</v>
+        <v>48</v>
+      </c>
+      <c r="P64" t="s">
+        <v>29</v>
+      </c>
+      <c r="X64" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="65">
@@ -2414,7 +2477,7 @@
         <v>2</v>
       </c>
       <c r="C65" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D65">
         <v>3</v>
@@ -2423,25 +2486,25 @@
         <v>1</v>
       </c>
       <c r="G65" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H65" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I65" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J65">
         <v>4</v>
       </c>
       <c r="K65" t="s">
-        <v>43</v>
-      </c>
-      <c r="S65" t="s">
-        <v>45</v>
-      </c>
-      <c r="T65" t="s">
-        <v>46</v>
+        <v>48</v>
+      </c>
+      <c r="X65" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="66">
@@ -2452,7 +2515,7 @@
         <v>2</v>
       </c>
       <c r="C66" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -2461,28 +2524,28 @@
         <v>10</v>
       </c>
       <c r="G66" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H66" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I66" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J66">
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>31</v>
-      </c>
-      <c r="S66" t="s">
-        <v>54</v>
-      </c>
-      <c r="T66" t="s">
-        <v>77</v>
-      </c>
-      <c r="V66" t="s">
-        <v>42</v>
+        <v>36</v>
+      </c>
+      <c r="X66" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA66" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="67">
@@ -2493,7 +2556,7 @@
         <v>2</v>
       </c>
       <c r="C67" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D67">
         <v>2</v>
@@ -2502,25 +2565,25 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H67" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I67" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J67">
         <v>-3</v>
       </c>
       <c r="K67" t="s">
-        <v>31</v>
-      </c>
-      <c r="S67" t="s">
-        <v>32</v>
-      </c>
-      <c r="T67" t="s">
-        <v>33</v>
+        <v>36</v>
+      </c>
+      <c r="X67" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="68">
@@ -2531,7 +2594,7 @@
         <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D68">
         <v>3</v>
@@ -2543,25 +2606,28 @@
         <v>-33</v>
       </c>
       <c r="G68" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H68" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I68" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="J68">
         <v>57</v>
       </c>
       <c r="K68" t="s">
-        <v>43</v>
-      </c>
-      <c r="S68" t="s">
-        <v>52</v>
-      </c>
-      <c r="T68" t="s">
-        <v>53</v>
+        <v>48</v>
+      </c>
+      <c r="P68" t="s">
+        <v>85</v>
+      </c>
+      <c r="X68" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="69">
@@ -2572,7 +2638,7 @@
         <v>2</v>
       </c>
       <c r="C69" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -2584,16 +2650,16 @@
         <v>-10</v>
       </c>
       <c r="G69" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H69" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I69" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K69" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="70">
@@ -2604,7 +2670,7 @@
         <v>2</v>
       </c>
       <c r="C70" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D70">
         <v>2</v>
@@ -2613,13 +2679,13 @@
         <v>8</v>
       </c>
       <c r="G70" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H70" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I70" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="71">
@@ -2630,7 +2696,7 @@
         <v>2</v>
       </c>
       <c r="C71" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D71">
         <v>3</v>
@@ -2639,13 +2705,13 @@
         <v>7</v>
       </c>
       <c r="G71" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H71" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I71" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="72">
@@ -2656,7 +2722,7 @@
         <v>2</v>
       </c>
       <c r="C72" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D72">
         <v>4</v>
@@ -2665,13 +2731,13 @@
         <v>7</v>
       </c>
       <c r="G72" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H72" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I72" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="73">
@@ -2682,7 +2748,7 @@
         <v>2</v>
       </c>
       <c r="C73" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -2694,25 +2760,25 @@
         <v>-20</v>
       </c>
       <c r="G73" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H73" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I73" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="J73">
         <v>13</v>
       </c>
       <c r="K73" t="s">
-        <v>43</v>
-      </c>
-      <c r="S73" t="s">
-        <v>54</v>
-      </c>
-      <c r="T73" t="s">
-        <v>81</v>
+        <v>48</v>
+      </c>
+      <c r="X73" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="74">
@@ -2723,7 +2789,7 @@
         <v>2</v>
       </c>
       <c r="C74" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -2735,25 +2801,28 @@
         <v>-33</v>
       </c>
       <c r="G74" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H74" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I74" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J74">
         <v>2</v>
       </c>
       <c r="K74" t="s">
-        <v>31</v>
-      </c>
-      <c r="S74" t="s">
-        <v>45</v>
-      </c>
-      <c r="T74" t="s">
-        <v>46</v>
+        <v>36</v>
+      </c>
+      <c r="P74" t="s">
+        <v>29</v>
+      </c>
+      <c r="X74" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="75">
@@ -2764,7 +2833,7 @@
         <v>2</v>
       </c>
       <c r="C75" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D75">
         <v>2</v>
@@ -2776,25 +2845,25 @@
         <v>-35</v>
       </c>
       <c r="G75" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H75" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I75" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J75">
         <v>1</v>
       </c>
       <c r="K75" t="s">
-        <v>31</v>
-      </c>
-      <c r="S75" t="s">
         <v>36</v>
       </c>
-      <c r="T75" t="s">
-        <v>82</v>
+      <c r="X75" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="76">
@@ -2805,7 +2874,7 @@
         <v>2</v>
       </c>
       <c r="C76" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D76">
         <v>3</v>
@@ -2817,28 +2886,31 @@
         <v>-35</v>
       </c>
       <c r="G76" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H76" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I76" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J76">
         <v>16</v>
       </c>
       <c r="K76" t="s">
-        <v>43</v>
-      </c>
-      <c r="S76" t="s">
-        <v>49</v>
-      </c>
-      <c r="T76" t="s">
-        <v>83</v>
-      </c>
-      <c r="V76" t="s">
-        <v>25</v>
+        <v>48</v>
+      </c>
+      <c r="P76" t="s">
+        <v>29</v>
+      </c>
+      <c r="X76" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA76" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="77">
@@ -2849,7 +2921,7 @@
         <v>2</v>
       </c>
       <c r="C77" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -2861,13 +2933,13 @@
         <v>49</v>
       </c>
       <c r="G77" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H77" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I77" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="78">
@@ -2878,7 +2950,7 @@
         <v>3</v>
       </c>
       <c r="C78" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -2887,13 +2959,13 @@
         <v>10</v>
       </c>
       <c r="G78" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H78" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I78" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="79">
@@ -2904,7 +2976,7 @@
         <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -2913,13 +2985,13 @@
         <v>10</v>
       </c>
       <c r="G79" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H79" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I79" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="80">
@@ -2930,7 +3002,7 @@
         <v>3</v>
       </c>
       <c r="C80" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -2939,13 +3011,13 @@
         <v>4</v>
       </c>
       <c r="G80" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H80" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I80" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="81">
@@ -2956,7 +3028,7 @@
         <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D81">
         <v>2</v>
@@ -2965,7 +3037,7 @@
         <v>4</v>
       </c>
       <c r="G81" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="82">
@@ -2976,7 +3048,7 @@
         <v>3</v>
       </c>
       <c r="C82" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D82">
         <v>2</v>
@@ -2985,13 +3057,13 @@
         <v>4</v>
       </c>
       <c r="G82" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H82" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I82" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="83">
@@ -3002,7 +3074,7 @@
         <v>3</v>
       </c>
       <c r="C83" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -3011,13 +3083,13 @@
         <v>10</v>
       </c>
       <c r="G83" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H83" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I83" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="84">
@@ -3028,7 +3100,7 @@
         <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -3037,13 +3109,13 @@
         <v>10</v>
       </c>
       <c r="G84" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H84" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I84" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="85">
@@ -3054,7 +3126,7 @@
         <v>3</v>
       </c>
       <c r="C85" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D85">
         <v>2</v>
@@ -3063,13 +3135,13 @@
         <v>10</v>
       </c>
       <c r="G85" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H85" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I85" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="86">
@@ -3080,7 +3152,7 @@
         <v>3</v>
       </c>
       <c r="C86" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -3089,13 +3161,13 @@
         <v>10</v>
       </c>
       <c r="G86" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H86" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I86" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="87">
@@ -3106,7 +3178,7 @@
         <v>3</v>
       </c>
       <c r="C87" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -3115,13 +3187,13 @@
         <v>10</v>
       </c>
       <c r="G87" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H87" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I87" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="88">
@@ -3132,7 +3204,7 @@
         <v>3</v>
       </c>
       <c r="C88" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -3141,28 +3213,28 @@
         <v>6</v>
       </c>
       <c r="G88" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H88" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I88" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J88">
         <v>4</v>
       </c>
       <c r="K88" t="s">
-        <v>43</v>
-      </c>
-      <c r="S88" t="s">
-        <v>54</v>
-      </c>
-      <c r="T88" t="s">
-        <v>86</v>
-      </c>
-      <c r="V88" t="s">
-        <v>42</v>
+        <v>48</v>
+      </c>
+      <c r="X88" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y88" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA88" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="89">
@@ -3173,7 +3245,7 @@
         <v>3</v>
       </c>
       <c r="C89" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -3182,25 +3254,28 @@
         <v>10</v>
       </c>
       <c r="G89" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H89" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I89" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J89">
         <v>7</v>
       </c>
       <c r="K89" t="s">
-        <v>43</v>
-      </c>
-      <c r="S89" t="s">
-        <v>36</v>
-      </c>
-      <c r="T89" t="s">
-        <v>87</v>
+        <v>48</v>
+      </c>
+      <c r="P89" t="s">
+        <v>29</v>
+      </c>
+      <c r="X89" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y89" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="90">
@@ -3211,7 +3286,7 @@
         <v>3</v>
       </c>
       <c r="C90" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -3220,25 +3295,25 @@
         <v>10</v>
       </c>
       <c r="G90" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H90" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I90" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J90">
         <v>3</v>
       </c>
       <c r="K90" t="s">
-        <v>31</v>
-      </c>
-      <c r="S90" t="s">
-        <v>47</v>
-      </c>
-      <c r="T90" t="s">
-        <v>70</v>
+        <v>36</v>
+      </c>
+      <c r="X90" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="91">
@@ -3249,7 +3324,7 @@
         <v>3</v>
       </c>
       <c r="C91" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D91">
         <v>2</v>
@@ -3258,25 +3333,28 @@
         <v>8</v>
       </c>
       <c r="G91" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H91" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I91" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J91">
         <v>2</v>
       </c>
       <c r="K91" t="s">
-        <v>31</v>
-      </c>
-      <c r="S91" t="s">
         <v>36</v>
       </c>
-      <c r="T91" t="s">
-        <v>82</v>
+      <c r="P91" t="s">
+        <v>29</v>
+      </c>
+      <c r="X91" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y91" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="92">
@@ -3287,7 +3365,7 @@
         <v>3</v>
       </c>
       <c r="C92" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D92">
         <v>3</v>
@@ -3299,28 +3377,31 @@
         <v>-35</v>
       </c>
       <c r="G92" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H92" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I92" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="J92">
         <v>65</v>
       </c>
       <c r="K92" t="s">
-        <v>43</v>
-      </c>
-      <c r="S92" t="s">
-        <v>49</v>
-      </c>
-      <c r="T92" t="s">
-        <v>75</v>
-      </c>
-      <c r="V92" t="s">
-        <v>42</v>
+        <v>48</v>
+      </c>
+      <c r="P92" t="s">
+        <v>29</v>
+      </c>
+      <c r="X92" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y92" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA92" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="93">
@@ -3331,7 +3412,7 @@
         <v>3</v>
       </c>
       <c r="C93" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -3343,28 +3424,31 @@
         <v>3</v>
       </c>
       <c r="G93" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H93" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="I93" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J93">
         <v>3</v>
       </c>
       <c r="K93" t="s">
-        <v>43</v>
-      </c>
-      <c r="S93" t="s">
-        <v>36</v>
-      </c>
-      <c r="T93" t="s">
-        <v>89</v>
-      </c>
-      <c r="V93" t="s">
-        <v>42</v>
+        <v>48</v>
+      </c>
+      <c r="P93" t="s">
+        <v>29</v>
+      </c>
+      <c r="X93" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y93" t="s">
+        <v>95</v>
+      </c>
+      <c r="AA93" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="94">
@@ -3375,7 +3459,7 @@
         <v>3</v>
       </c>
       <c r="C94" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -3384,13 +3468,13 @@
         <v>10</v>
       </c>
       <c r="G94" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H94" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I94" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="95">
@@ -3401,7 +3485,7 @@
         <v>3</v>
       </c>
       <c r="C95" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -3410,13 +3494,13 @@
         <v>12</v>
       </c>
       <c r="G95" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H95" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I95" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="96">
@@ -3427,7 +3511,7 @@
         <v>3</v>
       </c>
       <c r="C96" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D96">
         <v>2</v>
@@ -3436,13 +3520,13 @@
         <v>12</v>
       </c>
       <c r="G96" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H96" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I96" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="97">
@@ -3453,7 +3537,7 @@
         <v>3</v>
       </c>
       <c r="C97" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D97">
         <v>3</v>
@@ -3462,13 +3546,13 @@
         <v>12</v>
       </c>
       <c r="G97" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H97" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I97" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="98">
@@ -3479,7 +3563,7 @@
         <v>3</v>
       </c>
       <c r="C98" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -3488,13 +3572,13 @@
         <v>10</v>
       </c>
       <c r="G98" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H98" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I98" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="99">
@@ -3505,7 +3589,7 @@
         <v>3</v>
       </c>
       <c r="C99" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -3514,13 +3598,13 @@
         <v>10</v>
       </c>
       <c r="G99" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H99" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I99" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="100">
@@ -3531,7 +3615,7 @@
         <v>3</v>
       </c>
       <c r="C100" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -3540,13 +3624,13 @@
         <v>10</v>
       </c>
       <c r="G100" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H100" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I100" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="101">
@@ -3557,7 +3641,7 @@
         <v>3</v>
       </c>
       <c r="C101" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D101">
         <v>2</v>
@@ -3566,7 +3650,7 @@
         <v>3</v>
       </c>
       <c r="G101" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="102">
@@ -3577,7 +3661,7 @@
         <v>3</v>
       </c>
       <c r="C102" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -3586,13 +3670,13 @@
         <v>10</v>
       </c>
       <c r="G102" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H102" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I102" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="103">
@@ -3603,7 +3687,7 @@
         <v>3</v>
       </c>
       <c r="C103" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D103">
         <v>2</v>
@@ -3612,13 +3696,13 @@
         <v>10</v>
       </c>
       <c r="G103" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H103" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I103" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="104">
@@ -3629,7 +3713,7 @@
         <v>3</v>
       </c>
       <c r="C104" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D104">
         <v>3</v>
@@ -3638,13 +3722,13 @@
         <v>8</v>
       </c>
       <c r="G104" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H104" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I104" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="105">
@@ -3655,7 +3739,7 @@
         <v>3</v>
       </c>
       <c r="C105" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D105">
         <v>4</v>
@@ -3664,15 +3748,15 @@
         <v>12</v>
       </c>
       <c r="G105" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H105" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I105" t="s">
-        <v>76</v>
-      </c>
-      <c r="W105">
+        <v>81</v>
+      </c>
+      <c r="AB105">
         <v>9</v>
       </c>
     </row>
@@ -3684,7 +3768,7 @@
         <v>3</v>
       </c>
       <c r="C106" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -3696,30 +3780,30 @@
         <v>-3</v>
       </c>
       <c r="G106" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H106" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I106" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J106">
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>31</v>
-      </c>
-      <c r="S106" t="s">
-        <v>54</v>
-      </c>
-      <c r="T106" t="s">
-        <v>72</v>
-      </c>
-      <c r="V106" t="s">
-        <v>25</v>
-      </c>
-      <c r="W106">
+        <v>36</v>
+      </c>
+      <c r="X106" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y106" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA106" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB106">
         <v>8</v>
       </c>
     </row>
@@ -3731,7 +3815,7 @@
         <v>3</v>
       </c>
       <c r="C107" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D107">
         <v>2</v>
@@ -3743,27 +3827,30 @@
         <v>-3</v>
       </c>
       <c r="G107" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H107" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I107" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J107">
         <v>5</v>
       </c>
       <c r="K107" t="s">
-        <v>43</v>
-      </c>
-      <c r="S107" t="s">
-        <v>36</v>
-      </c>
-      <c r="T107" t="s">
-        <v>59</v>
-      </c>
-      <c r="W107">
+        <v>48</v>
+      </c>
+      <c r="P107" t="s">
+        <v>29</v>
+      </c>
+      <c r="X107" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y107" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB107">
         <v>8</v>
       </c>
     </row>
@@ -3775,7 +3862,7 @@
         <v>3</v>
       </c>
       <c r="C108" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D108">
         <v>3</v>
@@ -3787,28 +3874,31 @@
         <v>-8</v>
       </c>
       <c r="G108" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H108" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I108" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="J108">
         <v>13</v>
       </c>
       <c r="K108" t="s">
-        <v>43</v>
-      </c>
-      <c r="S108" t="s">
-        <v>52</v>
-      </c>
-      <c r="T108" t="s">
-        <v>90</v>
-      </c>
-      <c r="V108" t="s">
-        <v>42</v>
+        <v>48</v>
+      </c>
+      <c r="P108" t="s">
+        <v>85</v>
+      </c>
+      <c r="X108" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y108" t="s">
+        <v>96</v>
+      </c>
+      <c r="AA108" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="109">
@@ -3819,7 +3909,7 @@
         <v>3</v>
       </c>
       <c r="C109" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D109">
         <v>1</v>
@@ -3831,25 +3921,28 @@
         <v>-21</v>
       </c>
       <c r="G109" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H109" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I109" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J109">
         <v>13</v>
       </c>
       <c r="K109" t="s">
-        <v>43</v>
-      </c>
-      <c r="S109" t="s">
-        <v>36</v>
-      </c>
-      <c r="T109" t="s">
-        <v>33</v>
+        <v>48</v>
+      </c>
+      <c r="P109" t="s">
+        <v>29</v>
+      </c>
+      <c r="X109" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y109" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="110">
@@ -3860,7 +3953,7 @@
         <v>3</v>
       </c>
       <c r="C110" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D110">
         <v>1</v>
@@ -3872,25 +3965,25 @@
         <v>-34</v>
       </c>
       <c r="G110" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H110" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I110" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J110">
         <v>4</v>
       </c>
       <c r="K110" t="s">
-        <v>43</v>
-      </c>
-      <c r="S110" t="s">
-        <v>47</v>
-      </c>
-      <c r="T110" t="s">
         <v>48</v>
+      </c>
+      <c r="X110" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y110" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="111">
@@ -3901,7 +3994,7 @@
         <v>3</v>
       </c>
       <c r="C111" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D111">
         <v>2</v>
@@ -3913,25 +4006,28 @@
         <v>-38</v>
       </c>
       <c r="G111" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H111" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I111" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J111">
         <v>20</v>
       </c>
       <c r="K111" t="s">
-        <v>43</v>
-      </c>
-      <c r="S111" t="s">
-        <v>36</v>
-      </c>
-      <c r="T111" t="s">
-        <v>33</v>
+        <v>48</v>
+      </c>
+      <c r="P111" t="s">
+        <v>29</v>
+      </c>
+      <c r="X111" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y111" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="112">
@@ -3942,7 +4038,7 @@
         <v>3</v>
       </c>
       <c r="C112" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -3954,7 +4050,7 @@
         <v>42</v>
       </c>
       <c r="G112" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="113">
@@ -3965,7 +4061,7 @@
         <v>3</v>
       </c>
       <c r="C113" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -3974,25 +4070,28 @@
         <v>10</v>
       </c>
       <c r="G113" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H113" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I113" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J113">
         <v>3</v>
       </c>
       <c r="K113" t="s">
-        <v>31</v>
-      </c>
-      <c r="S113" t="s">
         <v>36</v>
       </c>
-      <c r="T113" t="s">
-        <v>33</v>
+      <c r="P113" t="s">
+        <v>29</v>
+      </c>
+      <c r="X113" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y113" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="114">
@@ -4003,7 +4102,7 @@
         <v>4</v>
       </c>
       <c r="C114" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D114">
         <v>2</v>
@@ -4012,25 +4111,25 @@
         <v>8</v>
       </c>
       <c r="G114" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H114" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I114" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J114">
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>31</v>
-      </c>
-      <c r="S114" t="s">
-        <v>47</v>
-      </c>
-      <c r="T114" t="s">
-        <v>70</v>
+        <v>36</v>
+      </c>
+      <c r="X114" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y114" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="115">
@@ -4041,7 +4140,7 @@
         <v>4</v>
       </c>
       <c r="C115" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D115">
         <v>3</v>
@@ -4053,25 +4152,28 @@
         <v>27</v>
       </c>
       <c r="G115" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H115" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I115" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="J115">
         <v>-8</v>
       </c>
       <c r="K115" t="s">
-        <v>31</v>
-      </c>
-      <c r="S115" t="s">
         <v>36</v>
       </c>
-      <c r="T115" t="s">
-        <v>37</v>
+      <c r="P115" t="s">
+        <v>29</v>
+      </c>
+      <c r="X115" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y115" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="116">
@@ -4082,7 +4184,7 @@
         <v>4</v>
       </c>
       <c r="C116" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D116">
         <v>4</v>
@@ -4094,13 +4196,13 @@
         <v>35</v>
       </c>
       <c r="G116" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H116" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I116" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="117">
@@ -4111,7 +4213,7 @@
         <v>4</v>
       </c>
       <c r="C117" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -4120,13 +4222,13 @@
         <v>10</v>
       </c>
       <c r="G117" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H117" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I117" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="118">
@@ -4137,7 +4239,7 @@
         <v>4</v>
       </c>
       <c r="C118" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D118">
         <v>2</v>
@@ -4146,13 +4248,13 @@
         <v>4</v>
       </c>
       <c r="G118" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H118" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I118" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="119">
@@ -4163,7 +4265,7 @@
         <v>4</v>
       </c>
       <c r="C119" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D119">
         <v>3</v>
@@ -4172,13 +4274,13 @@
         <v>4</v>
       </c>
       <c r="G119" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H119" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I119" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="120">
@@ -4189,7 +4291,7 @@
         <v>4</v>
       </c>
       <c r="C120" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D120">
         <v>4</v>
@@ -4198,13 +4300,13 @@
         <v>15</v>
       </c>
       <c r="G120" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H120" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I120" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="121">
@@ -4215,7 +4317,7 @@
         <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -4224,25 +4326,25 @@
         <v>10</v>
       </c>
       <c r="G121" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H121" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I121" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J121">
         <v>1</v>
       </c>
       <c r="K121" t="s">
-        <v>31</v>
-      </c>
-      <c r="S121" t="s">
-        <v>47</v>
-      </c>
-      <c r="T121" t="s">
-        <v>70</v>
+        <v>36</v>
+      </c>
+      <c r="X121" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y121" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="122">
@@ -4253,7 +4355,7 @@
         <v>4</v>
       </c>
       <c r="C122" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D122">
         <v>2</v>
@@ -4265,25 +4367,25 @@
         <v>40</v>
       </c>
       <c r="G122" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H122" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I122" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J122">
         <v>0</v>
       </c>
       <c r="K122" t="s">
-        <v>31</v>
-      </c>
-      <c r="S122" t="s">
-        <v>54</v>
-      </c>
-      <c r="T122" t="s">
-        <v>91</v>
+        <v>36</v>
+      </c>
+      <c r="X122" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y122" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="123">
@@ -4294,7 +4396,7 @@
         <v>4</v>
       </c>
       <c r="C123" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D123">
         <v>3</v>
@@ -4306,28 +4408,28 @@
         <v>40</v>
       </c>
       <c r="G123" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H123" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I123" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="J123">
         <v>40</v>
       </c>
       <c r="K123" t="s">
-        <v>43</v>
-      </c>
-      <c r="S123" t="s">
-        <v>49</v>
-      </c>
-      <c r="T123" t="s">
-        <v>92</v>
-      </c>
-      <c r="V123" t="s">
-        <v>25</v>
+        <v>48</v>
+      </c>
+      <c r="X123" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y123" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA123" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="124">
@@ -4338,7 +4440,7 @@
         <v>4</v>
       </c>
       <c r="C124" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -4350,13 +4452,13 @@
         <v>3</v>
       </c>
       <c r="G124" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H124" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I124" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="125">
@@ -4367,7 +4469,7 @@
         <v>4</v>
       </c>
       <c r="C125" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D125">
         <v>1</v>
@@ -4376,13 +4478,13 @@
         <v>10</v>
       </c>
       <c r="G125" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H125" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I125" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="126">
@@ -4393,7 +4495,7 @@
         <v>4</v>
       </c>
       <c r="C126" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -4402,13 +4504,13 @@
         <v>14</v>
       </c>
       <c r="G126" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H126" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I126" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="127">
@@ -4419,7 +4521,7 @@
         <v>4</v>
       </c>
       <c r="C127" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D127">
         <v>2</v>
@@ -4428,13 +4530,13 @@
         <v>14</v>
       </c>
       <c r="G127" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H127" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I127" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="128">
@@ -4445,7 +4547,7 @@
         <v>4</v>
       </c>
       <c r="C128" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D128">
         <v>3</v>
@@ -4454,13 +4556,13 @@
         <v>14</v>
       </c>
       <c r="G128" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H128" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I128" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="129">
@@ -4471,7 +4573,7 @@
         <v>4</v>
       </c>
       <c r="C129" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D129">
         <v>4</v>
@@ -4480,13 +4582,13 @@
         <v>14</v>
       </c>
       <c r="G129" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H129" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I129" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="130">
@@ -4497,7 +4599,7 @@
         <v>4</v>
       </c>
       <c r="C130" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D130">
         <v>1</v>
@@ -4506,30 +4608,30 @@
         <v>10</v>
       </c>
       <c r="G130" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H130" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I130" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J130">
         <v>48</v>
       </c>
       <c r="K130" t="s">
-        <v>43</v>
-      </c>
-      <c r="S130" t="s">
-        <v>54</v>
-      </c>
-      <c r="T130" t="s">
-        <v>93</v>
-      </c>
-      <c r="V130" t="s">
-        <v>25</v>
-      </c>
-      <c r="W130">
+        <v>48</v>
+      </c>
+      <c r="X130" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y130" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA130" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB130">
         <v>1</v>
       </c>
     </row>
@@ -4541,7 +4643,7 @@
         <v>4</v>
       </c>
       <c r="C131" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D131">
         <v>1</v>
@@ -4550,18 +4652,18 @@
         <v>9</v>
       </c>
       <c r="G131" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I131" t="s">
-        <v>94</v>
-      </c>
-      <c r="S131" t="s">
-        <v>47</v>
-      </c>
-      <c r="T131" t="s">
-        <v>95</v>
-      </c>
-      <c r="W131">
+        <v>100</v>
+      </c>
+      <c r="X131" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y131" t="s">
+        <v>101</v>
+      </c>
+      <c r="AB131">
         <v>1</v>
       </c>
     </row>
@@ -4573,7 +4675,7 @@
         <v>4</v>
       </c>
       <c r="C132" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D132">
         <v>1</v>
@@ -4582,27 +4684,27 @@
         <v>9</v>
       </c>
       <c r="G132" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H132" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I132" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J132">
         <v>4</v>
       </c>
       <c r="K132" t="s">
-        <v>43</v>
-      </c>
-      <c r="S132" t="s">
-        <v>54</v>
-      </c>
-      <c r="T132" t="s">
-        <v>93</v>
-      </c>
-      <c r="W132">
+        <v>48</v>
+      </c>
+      <c r="X132" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y132" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB132">
         <v>1</v>
       </c>
     </row>
@@ -4614,7 +4716,7 @@
         <v>4</v>
       </c>
       <c r="C133" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D133">
         <v>2</v>
@@ -4623,28 +4725,28 @@
         <v>5</v>
       </c>
       <c r="G133" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H133" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I133" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J133">
         <v>1</v>
       </c>
       <c r="K133" t="s">
-        <v>31</v>
-      </c>
-      <c r="S133" t="s">
-        <v>54</v>
-      </c>
-      <c r="T133" t="s">
-        <v>93</v>
-      </c>
-      <c r="V133" t="s">
-        <v>25</v>
+        <v>36</v>
+      </c>
+      <c r="X133" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y133" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA133" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="134">
@@ -4655,7 +4757,7 @@
         <v>4</v>
       </c>
       <c r="C134" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D134">
         <v>3</v>
@@ -4667,25 +4769,25 @@
         <v>4</v>
       </c>
       <c r="G134" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H134" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I134" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J134">
         <v>0</v>
       </c>
       <c r="K134" t="s">
-        <v>31</v>
-      </c>
-      <c r="S134" t="s">
-        <v>96</v>
-      </c>
-      <c r="T134" t="s">
-        <v>97</v>
+        <v>36</v>
+      </c>
+      <c r="X134" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y134" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="135">
@@ -4696,7 +4798,7 @@
         <v>4</v>
       </c>
       <c r="C135" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D135">
         <v>4</v>
@@ -4708,13 +4810,13 @@
         <v>4</v>
       </c>
       <c r="G135" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H135" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I135" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="136">
@@ -4725,7 +4827,7 @@
         <v>4</v>
       </c>
       <c r="C136" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D136">
         <v>1</v>
@@ -4734,13 +4836,13 @@
         <v>10</v>
       </c>
       <c r="G136" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H136" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I136" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="137">
@@ -4751,7 +4853,7 @@
         <v>4</v>
       </c>
       <c r="C137" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D137">
         <v>1</v>
@@ -4760,13 +4862,13 @@
         <v>10</v>
       </c>
       <c r="G137" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H137" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I137" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="138">
@@ -4777,7 +4879,7 @@
         <v>4</v>
       </c>
       <c r="C138" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D138">
         <v>1</v>
@@ -4786,13 +4888,13 @@
         <v>10</v>
       </c>
       <c r="G138" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H138" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I138" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="139">
@@ -4803,7 +4905,7 @@
         <v>4</v>
       </c>
       <c r="C139" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D139">
         <v>1</v>
@@ -4812,13 +4914,13 @@
         <v>10</v>
       </c>
       <c r="G139" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H139" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I139" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="140">
@@ -4829,7 +4931,7 @@
         <v>4</v>
       </c>
       <c r="C140" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D140">
         <v>1</v>
@@ -4838,28 +4940,28 @@
         <v>10</v>
       </c>
       <c r="G140" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H140" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I140" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J140">
         <v>1</v>
       </c>
       <c r="K140" t="s">
-        <v>31</v>
-      </c>
-      <c r="S140" t="s">
-        <v>54</v>
-      </c>
-      <c r="T140" t="s">
-        <v>93</v>
-      </c>
-      <c r="V140" t="s">
-        <v>25</v>
+        <v>36</v>
+      </c>
+      <c r="X140" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y140" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA140" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="141">
@@ -4870,7 +4972,7 @@
         <v>4</v>
       </c>
       <c r="C141" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D141">
         <v>2</v>
@@ -4882,25 +4984,25 @@
         <v>-21</v>
       </c>
       <c r="G141" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H141" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I141" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J141">
         <v>60</v>
       </c>
       <c r="K141" t="s">
-        <v>43</v>
-      </c>
-      <c r="S141" t="s">
-        <v>47</v>
-      </c>
-      <c r="T141" t="s">
-        <v>98</v>
+        <v>48</v>
+      </c>
+      <c r="X141" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y141" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="142">
@@ -4911,7 +5013,7 @@
         <v>4</v>
       </c>
       <c r="C142" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -4923,25 +5025,25 @@
         <v>19</v>
       </c>
       <c r="G142" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H142" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I142" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J142">
         <v>2</v>
       </c>
       <c r="K142" t="s">
-        <v>31</v>
-      </c>
-      <c r="S142" t="s">
-        <v>54</v>
-      </c>
-      <c r="T142" t="s">
-        <v>99</v>
+        <v>36</v>
+      </c>
+      <c r="X142" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y142" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="143">
@@ -4952,7 +5054,7 @@
         <v>4</v>
       </c>
       <c r="C143" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D143">
         <v>2</v>
@@ -4964,25 +5066,28 @@
         <v>17</v>
       </c>
       <c r="G143" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H143" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I143" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J143">
         <v>0</v>
       </c>
       <c r="K143" t="s">
-        <v>31</v>
-      </c>
-      <c r="S143" t="s">
         <v>36</v>
       </c>
-      <c r="T143" t="s">
-        <v>74</v>
+      <c r="P143" t="s">
+        <v>29</v>
+      </c>
+      <c r="X143" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y143" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="144">
@@ -4993,7 +5098,7 @@
         <v>4</v>
       </c>
       <c r="C144" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D144">
         <v>3</v>
@@ -5005,28 +5110,28 @@
         <v>17</v>
       </c>
       <c r="G144" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H144" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I144" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J144">
         <v>5</v>
       </c>
       <c r="K144" t="s">
-        <v>43</v>
-      </c>
-      <c r="S144" t="s">
-        <v>54</v>
-      </c>
-      <c r="T144" t="s">
-        <v>93</v>
-      </c>
-      <c r="V144" t="s">
-        <v>42</v>
+        <v>48</v>
+      </c>
+      <c r="X144" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y144" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA144" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="145">
@@ -5037,7 +5142,7 @@
         <v>4</v>
       </c>
       <c r="C145" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D145">
         <v>4</v>
@@ -5046,13 +5151,13 @@
         <v>5</v>
       </c>
       <c r="G145" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H145" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I145" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="146">
@@ -5063,7 +5168,7 @@
         <v>4</v>
       </c>
       <c r="C146" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D146">
         <v>1</v>
@@ -5072,13 +5177,13 @@
         <v>10</v>
       </c>
       <c r="G146" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H146" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I146" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="147">
@@ -5089,7 +5194,7 @@
         <v>4</v>
       </c>
       <c r="C147" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D147">
         <v>1</v>
@@ -5098,13 +5203,13 @@
         <v>10</v>
       </c>
       <c r="G147" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H147" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I147" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="148">
@@ -5115,7 +5220,7 @@
         <v>4</v>
       </c>
       <c r="C148" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D148">
         <v>2</v>
@@ -5124,13 +5229,13 @@
         <v>10</v>
       </c>
       <c r="G148" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H148" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I148" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="149">
@@ -5141,7 +5246,7 @@
         <v>4</v>
       </c>
       <c r="C149" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D149">
         <v>1</v>
@@ -5150,13 +5255,13 @@
         <v>10</v>
       </c>
       <c r="G149" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H149" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I149" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="150">
@@ -5167,7 +5272,7 @@
         <v>4</v>
       </c>
       <c r="C150" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D150">
         <v>2</v>
@@ -5176,13 +5281,13 @@
         <v>7</v>
       </c>
       <c r="G150" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H150" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I150" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="151">
@@ -5193,7 +5298,7 @@
         <v>4</v>
       </c>
       <c r="C151" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D151">
         <v>3</v>
@@ -5202,13 +5307,13 @@
         <v>7</v>
       </c>
       <c r="G151" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H151" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I151" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="152">
@@ -5219,7 +5324,7 @@
         <v>4</v>
       </c>
       <c r="C152" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D152">
         <v>4</v>
@@ -5228,13 +5333,13 @@
         <v>7</v>
       </c>
       <c r="G152" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H152" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I152" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="153">
@@ -5245,7 +5350,7 @@
         <v>4</v>
       </c>
       <c r="C153" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D153">
         <v>1</v>
@@ -5254,13 +5359,13 @@
         <v>10</v>
       </c>
       <c r="G153" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H153" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I153" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
